--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486753_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486753_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6589</v>
+        <v>5.1722</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6003</v>
+        <v>4.1384</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0586</v>
+        <v>1.0338</v>
       </c>
       <c r="G2" t="n">
         <v>2.5072</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2523</v>
+        <v>0.7655</v>
       </c>
       <c r="T2" t="n">
-        <v>0.965</v>
+        <v>0.5031</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2872</v>
+        <v>0.2624</v>
       </c>
       <c r="V2" t="n">
         <v>1.5133</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4247</v>
+        <v>1.9663</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9499</v>
+        <v>1.0809</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5252</v>
+        <v>0.8854</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3792</v>
+        <v>-0.2987</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5932</v>
+        <v>-1.3521</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.214</v>
+        <v>1.0534</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0286</v>
+        <v>1.2477</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9042</v>
+        <v>-0.1788</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1244</v>
+        <v>1.4265</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6494</v>
+        <v>-1.5464</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.311</v>
+        <v>-1.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3384</v>
+        <v>-0.3731</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3515</v>
+        <v>-1.5446</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0277</v>
+        <v>-0.4068</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.028</v>
+        <v>-0.4211</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004</v>
+        <v>0.0143</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6991000000000001</v>
+        <v>1.5133</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6991000000000001</v>
+        <v>1.7989</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.314</v>
+        <v>1.3765</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4534</v>
+        <v>1.9017</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8606</v>
+        <v>-0.5252</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2987</v>
+        <v>1.3792</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3521</v>
+        <v>2.5932</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0534</v>
+        <v>-1.214</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2477</v>
+        <v>4.0286</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1788</v>
+        <v>3.9042</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4265</v>
+        <v>0.1244</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5464</v>
+        <v>-2.6494</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1733</v>
+        <v>-1.311</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3731</v>
+        <v>-1.3384</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5446</v>
+        <v>-1.3515</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0591</v>
+        <v>-0.0759</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0486</v>
+        <v>-0.0762</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0105</v>
+        <v>0.0004</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5133</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7989</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.915</v>
+        <v>1.1604</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.512</v>
+        <v>-0.0432</v>
       </c>
       <c r="F5" t="n">
-        <v>1.427</v>
+        <v>1.2036</v>
       </c>
       <c r="G5" t="n">
         <v>0.8182</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7339</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2484</v>
+        <v>0.2205</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9823</v>
+        <v>0.7588</v>
       </c>
       <c r="V5" t="n">
         <v>0.3282</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3743</v>
+        <v>0.0362</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6397</v>
+        <v>-0.9093</v>
       </c>
       <c r="F6" t="n">
-        <v>1.014</v>
+        <v>0.9455</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6684</v>
+        <v>-0.9788</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6337</v>
+        <v>-0.9381</v>
       </c>
       <c r="I6" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.1593</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.0349</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1244</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.3515</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.9654</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.9535</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.8054</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.7589</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-1.6219</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.8283</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.7935</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1931</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-2.1239</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3169</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.0925</v>
+        <v>0.7447</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0832</v>
+        <v>0.2618</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1757</v>
+        <v>0.4829</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.243</v>
+        <v>0.6565</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8568</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0692</v>
+        <v>-0.1406</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7024</v>
+        <v>-1.478</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7716</v>
+        <v>1.3374</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9788</v>
+        <v>-0.0648</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9381</v>
+        <v>-1.0346</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0407</v>
+        <v>0.9698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1805</v>
+        <v>-0.2711</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0968</v>
+        <v>-0.2756</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0837</v>
+        <v>0.0046</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1593</v>
+        <v>0.2063</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0349</v>
+        <v>-0.759</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1244</v>
+        <v>0.9653</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4686</v>
+        <v>-0.0485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3091</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5557</v>
+        <v>-0.4975</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8435</v>
+        <v>-0.7914</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2877</v>
+        <v>0.2939</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0648</v>
+        <v>-0.6684</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0346</v>
+        <v>-1.6337</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9698</v>
+        <v>0.9654</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2711</v>
+        <v>0.9535</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2756</v>
+        <v>-0.8054</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0046</v>
+        <v>1.7589</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2063</v>
+        <v>-1.6219</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.759</v>
+        <v>-0.8283</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9653</v>
+        <v>-0.7935</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0883</v>
+        <v>0.2208</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4139</v>
+        <v>-0.2349</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5022</v>
+        <v>0.4556</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5045</v>
+        <v>-1.052</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1267</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3778</v>
+        <v>-0.9805</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5442</v>
@@ -1156,13 +1156,13 @@
         <v>2.3169</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7559</v>
+        <v>-0.3034</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0272</v>
+        <v>0.0824</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7831</v>
+        <v>-0.3858</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0318</v>
+        <v>-2.1613</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4469</v>
+        <v>-1.7503</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5848</v>
+        <v>-0.411</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3007</v>
@@ -1234,13 +1234,13 @@
         <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2537</v>
+        <v>0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5236</v>
+        <v>0.2203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2699</v>
+        <v>-0.0961</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5985</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6394</v>
+        <v>-2.2835</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8003</v>
+        <v>-0.5935</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8391</v>
+        <v>-1.6901</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5732</v>
@@ -1312,13 +1312,13 @@
         <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1269</v>
+        <v>0.4827</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0277</v>
+        <v>0.1792</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1545</v>
+        <v>0.3035</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.024699999999999</v>
+        <v>3.576699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9320999999999999</v>
+        <v>1.4838</v>
       </c>
       <c r="F12" t="n">
-        <v>2.092600000000001</v>
+        <v>2.0928</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2758000000000002</v>
+        <v>0.2757999999999997</v>
       </c>
       <c r="H12" t="n">
         <v>-2.414300000000001</v>
@@ -1366,7 +1366,7 @@
         <v>12.1132</v>
       </c>
       <c r="K12" t="n">
-        <v>7.591399999999999</v>
+        <v>7.591400000000001</v>
       </c>
       <c r="L12" t="n">
         <v>4.522</v>
@@ -1390,28 +1390,28 @@
         <v>14.4809</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4826</v>
+        <v>3.0345</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1346</v>
+        <v>0.6866000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>2.347900000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6990999999999996</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>2.1996</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8987</v>
+        <v>-2.898700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2936</v>
+        <v>6.823</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2862</v>
+        <v>3.1763</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9925</v>
+        <v>3.6467</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7752</v>
+        <v>3.779</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3103</v>
+        <v>2.6352</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4649</v>
+        <v>1.1439</v>
       </c>
       <c r="J13" t="n">
-        <v>8.4727</v>
+        <v>3.9045</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6211</v>
+        <v>3.7394</v>
       </c>
       <c r="L13" t="n">
-        <v>4.8515</v>
+        <v>0.1651</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6975</v>
+        <v>-0.1255</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3109</v>
+        <v>-1.1043</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3866</v>
+        <v>0.9788</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1585</v>
+        <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9046</v>
+        <v>0.1172</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7443</v>
+        <v>-0.1177</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1603</v>
+        <v>0.2348</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6138</v>
+        <v>2.5406</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6138</v>
+        <v>1.0273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1209</v>
+        <v>6.2095</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0728</v>
+        <v>6.9759</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0481</v>
+        <v>-0.7664</v>
       </c>
       <c r="G14" t="n">
-        <v>3.779</v>
+        <v>6.7752</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6352</v>
+        <v>2.3103</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1439</v>
+        <v>4.4649</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9045</v>
+        <v>8.4727</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7394</v>
+        <v>3.6211</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1651</v>
+        <v>4.8515</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1255</v>
+        <v>-1.6975</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1043</v>
+        <v>-1.3109</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9788</v>
+        <v>-0.3866</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5849</v>
+        <v>0.8205</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2211</v>
+        <v>0.434</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3638</v>
+        <v>0.3865</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5406</v>
+        <v>-0.6138</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.0273</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9439</v>
+        <v>1.8376</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2032</v>
+        <v>0.3066</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7407</v>
+        <v>1.531</v>
       </c>
       <c r="G15" t="n">
         <v>0.5243</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6787</v>
+        <v>0.5724</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5245</v>
+        <v>-0.4211</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2032</v>
+        <v>0.9935</v>
       </c>
       <c r="V15" t="n">
         <v>1.5133</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1325</v>
+        <v>0.0387</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3223</v>
+        <v>1.1154</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1898</v>
+        <v>-1.0767</v>
       </c>
       <c r="G16" t="n">
         <v>0.5049</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4304</v>
+        <v>-0.5241</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1383</v>
+        <v>-0.3451</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2921</v>
+        <v>-0.179</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3282</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4935</v>
+        <v>-0.6756</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8556</v>
+        <v>-2.0625</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3621</v>
+        <v>1.3869</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6078</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4578</v>
+        <v>0.2758</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0279</v>
+        <v>-0.2347</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4857</v>
+        <v>0.5105</v>
       </c>
       <c r="V17" t="n">
         <v>0.6565</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7245</v>
+        <v>-0.879</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9952</v>
+        <v>-1.2021</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2708</v>
+        <v>0.3231</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7065</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1764</v>
+        <v>-0.3309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.359</v>
+        <v>-0.5658</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1826</v>
+        <v>0.2349</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1024</v>
+        <v>-1.384</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8217</v>
+        <v>-2.3046</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.9206</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9122</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3253</v>
+        <v>0.3931</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6622</v>
+        <v>-0.1451</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3368</v>
+        <v>0.5381</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4474</v>
+        <v>-1.9536</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8841</v>
+        <v>-0.6772</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5633</v>
+        <v>-1.2764</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9398</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8937</v>
+        <v>-0.4</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3587</v>
+        <v>-0.1519</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.535</v>
+        <v>-0.2481</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5687</v>
+        <v>-3.5287</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9111</v>
+        <v>-1.2214</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6576</v>
+        <v>-2.3073</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7491</v>
@@ -2092,13 +2092,13 @@
         <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7504</v>
+        <v>-0.7104</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1107</v>
+        <v>-0.421</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6397</v>
+        <v>-0.2894</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8415</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.179399999999999</v>
+        <v>-7.4443</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5095</v>
+        <v>-6.1992</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6699</v>
+        <v>-1.2451</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9439</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3626</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6898</v>
+        <v>-0.3796</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6727</v>
+        <v>-0.248</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9421</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.024999999999999</v>
+        <v>-0.9564000000000004</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.092700000000001</v>
+        <v>-2.092799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9321000000000004</v>
+        <v>1.1364</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2759000000000009</v>
@@ -2248,13 +2248,13 @@
         <v>13.5155</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4826</v>
+        <v>-0.4139</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.3479</v>
+        <v>-2.348</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1347</v>
+        <v>1.9338</v>
       </c>
       <c r="V23" t="n">
         <v>0.6992000000000002</v>
